--- a/data/trans_orig/IP18A05-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP18A05-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97927</t>
+          <t>98152</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>206523</t>
+          <t>205863</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>598</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>228596</t>
+          <t>228255</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>229213</t>
+          <t>229209</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>459734</t>
+          <t>459112</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>464393</t>
+          <t>464391</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>728</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>100160</t>
+          <t>100702</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>110041</t>
+          <t>110851</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>213713</t>
+          <t>214157</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>220257</t>
+          <t>220263</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>482</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154354</t>
+          <t>153898</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163199</t>
+          <t>163705</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>320174</t>
+          <t>319808</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>325463</t>
+          <t>325465</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>589231</t>
+          <t>588920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>595987</t>
+          <t>595978</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>615442</t>
+          <t>615496</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>622634</t>
+          <t>622842</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1208191</t>
+          <t>1207998</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1217666</t>
+          <t>1217490</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>139815</t>
+          <t>138904</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>280723</t>
+          <t>280727</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11564</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>213826</t>
+          <t>214269</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>219201</t>
+          <t>219202</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>242738</t>
+          <t>242454</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>250458</t>
+          <t>249821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>460166</t>
+          <t>459809</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>468206</t>
+          <t>468372</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9997</t>
+          <t>9602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>142158</t>
+          <t>142522</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148884</t>
+          <t>148961</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144363</t>
+          <t>144346</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>289891</t>
+          <t>290286</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>297717</t>
+          <t>297768</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4513</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>158843</t>
+          <t>158441</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>311102</t>
+          <t>310551</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14013</t>
+          <t>14009</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20149</t>
+          <t>20865</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>653426</t>
+          <t>653253</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>661605</t>
+          <t>661085</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>692943</t>
+          <t>692947</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>702690</t>
+          <t>702844</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1350603</t>
+          <t>1349887</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1362056</t>
+          <t>1362207</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2720</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>124289</t>
+          <t>123882</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113312</t>
+          <t>113728</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>239719</t>
+          <t>239917</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11533</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>183637</t>
+          <t>183633</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>190821</t>
+          <t>190795</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>229761</t>
+          <t>230087</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>235574</t>
+          <t>235582</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>416783</t>
+          <t>416315</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>425644</t>
+          <t>425766</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6224</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>163274</t>
+          <t>163318</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>168867</t>
+          <t>168873</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>165205</t>
+          <t>165178</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>331333</t>
+          <t>331374</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>337063</t>
+          <t>337102</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>10922</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11730</t>
+          <t>11859</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>147438</t>
+          <t>147971</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136041</t>
+          <t>135925</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>144929</t>
+          <t>144723</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>286886</t>
+          <t>286757</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>296024</t>
+          <t>295821</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12783</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>10957</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25473</t>
+          <t>25045</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>627562</t>
+          <t>627299</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>636592</t>
+          <t>636653</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>653510</t>
+          <t>653672</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>664151</t>
+          <t>664668</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1284552</t>
+          <t>1284980</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1298611</t>
+          <t>1299068</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14249</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16584</t>
+          <t>16619</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32136</t>
+          <t>31650</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24216</t>
+          <t>24615</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30021</t>
+          <t>29328</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>55889</t>
+          <t>56272</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61280</t>
+          <t>61298</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5881</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>771</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27807</t>
+          <t>27516</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30990</t>
+          <t>31140</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61431</t>
+          <t>61113</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67382</t>
+          <t>67396</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>9092</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>546</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21891</t>
+          <t>21611</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35263</t>
+          <t>33454</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57393</t>
+          <t>58844</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66516</t>
+          <t>66525</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12147</t>
+          <t>12110</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>14847</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94027</t>
+          <t>93669</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99517</t>
+          <t>99164</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119445</t>
+          <t>119482</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129359</t>
+          <t>129204</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216887</t>
+          <t>217059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>227523</t>
+          <t>227611</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP18A05-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP18A05-Edad-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por dispensación de recetas en 2007 (tasa de respuesta: 99,73%)</t>
+          <t>Menores según si su última consulta médica fue por dispensación de recetas en 2007 (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,107 +723,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>711</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3562</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2866</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3942</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>107681</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>101003</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>98152</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>98848</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>101714</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,3%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,5%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,18%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>107681</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>316</t>
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>205863</t>
+          <t>205453</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>107681</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>107681</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>107681</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>101714</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>101714</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>101714</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>107681</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>107681</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>107681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1385</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4851</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3331</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2680</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1385</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4193</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>5922</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -1179,74 +1179,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>232017</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>228551</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>233402</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>345</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>230988</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>228255</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>228906</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>231586</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,74%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,84%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>232017</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>229209</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>233402</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>695</t>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>459112</t>
+          <t>459067</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>464391</t>
+          <t>464392</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>233402</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>233402</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>233402</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>346</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>231586</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>231586</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>231586</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>233402</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>233402</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>233402</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4768</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1523</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4618</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5253</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4820</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>114710</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>110903</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>115671</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,88%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>103797</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>100702</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>100067</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>105320</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,55%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,62%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,01%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>114710</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>110851</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>115671</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,83%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>327</t>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>214157</t>
+          <t>213477</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>115671</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>115671</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>115671</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>105320</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>105320</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>105320</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>115671</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>115671</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>115671</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1178</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>873</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4789</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4940</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1178</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3555</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>483</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>166082</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>163152</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>167260</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>157814</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>153898</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>153747</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>158687</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,45%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,89%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>166082</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>163705</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>167260</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,87%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>482</t>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>319808</t>
+          <t>320208</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>325465</t>
+          <t>325464</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>167260</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>167260</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>167260</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>158687</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>158687</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>158687</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>167260</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>167260</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>167260</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2100,67 +2100,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1386</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8710</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>3704</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1329</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8387</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8668</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3525</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1172</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8518</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13324</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>620489</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>615304</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>622628</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>886</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>593603</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>588920</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>595978</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>588639</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>595872</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,78%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>620489</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>615496</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>622842</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1207998</t>
+          <t>1208107</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1217490</t>
+          <t>1217554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>891</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>597307</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>597307</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>597307</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por dispensación de recetas en 2012 (tasa de respuesta: 98,05%)</t>
+          <t>Menores según si su última consulta médica fue por dispensación de recetas en 2012 (tasa de respuesta: 98,05%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,107 +2670,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>652</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3544</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3495</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3283</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -2783,74 +2783,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>141796</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>139176</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>142448</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,7%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>141562</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>141796</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>138904</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>142448</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,51%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>412</t>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>280727</t>
+          <t>280515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>142448</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>142448</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>142448</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>141562</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>141562</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>141562</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>142448</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>142448</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>142448</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4359</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9254</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2059</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>648</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5581</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5554</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4359</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9426</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11921</t>
+          <t>11846</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -3126,74 +3126,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>247521</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>242626</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>250377</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,33%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>313</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>217791</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>214269</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>214296</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>219202</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,06%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,47%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>247521</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>242454</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>249821</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,26%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>655</t>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>459809</t>
+          <t>459884</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>468372</t>
+          <t>468716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>251880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>251880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>251880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>316</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>219850</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>219850</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>219850</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>251880</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>251880</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>251880</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1527</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4825</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3553</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1253</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7692</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1248</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7378</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,37%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,83%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1527</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5328</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -3469,74 +3469,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>148147</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>144849</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>149674</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,78%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>146661</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>142522</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>148961</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>142836</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>148966</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,63%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,88%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,09%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>99,17%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>148147</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>144346</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>149674</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,98%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,44%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>421</t>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>290286</t>
+          <t>289798</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>297768</t>
+          <t>297815</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149674</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149674</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149674</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>150214</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>150214</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>150214</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149674</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149674</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149674</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,107 +3699,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4593</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4513</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4573</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -3812,74 +3812,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>161615</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>158361</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>162954</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,18%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>152170</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>161615</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>158441</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>162954</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,23%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>452</t>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>310551</t>
+          <t>309828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>162954</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>162954</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>162954</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>152170</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>152170</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>152170</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>162954</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>162954</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>162954</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7877</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4125</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>13234</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>5612</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2710</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10542</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2631</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>10814</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>7877</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4112</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>14009</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20865</t>
+          <t>20692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>699079</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>693722</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>702831</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>947</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>658183</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>653253</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>661085</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>652981</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>661164</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,15%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>993</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>699079</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>692947</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>702844</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1349887</t>
+          <t>1350060</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1362207</t>
+          <t>1362439</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>706956</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>706956</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>706956</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>955</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>663795</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>663795</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>663795</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>706956</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>706956</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>706956</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por dispensación de recetas en 2016 (tasa de respuesta: 98,16%)</t>
+          <t>Menores según si su última consulta médica fue por dispensación de recetas en 2016 (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4194</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>544</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3127</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3586</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1286</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4090</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>544</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>116532</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>113624</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>117818</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>126465</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>123882</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>123423</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>127009</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,57%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,18%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>116532</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>113728</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>117818</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,53%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>377</t>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>239917</t>
+          <t>239789</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>244286</t>
+          <t>244284</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>117818</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>117818</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>117818</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>127009</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>127009</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>127009</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>117818</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>117818</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>117818</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2285</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6421</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3650</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1273</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8435</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8168</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2285</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6161</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12001</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>233963</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>229827</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>235578</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,28%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>297</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>188418</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>183633</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>190795</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>183900</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>190835</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,1%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,61%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>233963</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>230087</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>235582</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>416315</t>
+          <t>416815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>425766</t>
+          <t>425743</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>236248</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>236248</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>236248</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>192068</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>192068</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>192068</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>236248</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>236248</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>236248</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3646</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2457</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6180</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5729</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3589</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -5416,74 +5416,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>168054</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>165121</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>168767</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,84%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>167041</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>163318</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>168873</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>163769</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>168867</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,55%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,35%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,62%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>99,63%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>168054</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>165178</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>168767</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,87%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>473</t>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>331374</t>
+          <t>330615</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>337102</t>
+          <t>337046</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168767</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168767</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168767</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>169498</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>169498</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>169498</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>168767</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>168767</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>168767</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5240</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2253</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10502</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,15%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>772</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3798</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3136</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,51%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5240</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2124</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>10922</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11859</t>
+          <t>11625</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -5759,74 +5759,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>141607</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>136345</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>144594</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,85%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,47%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>150997</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>147971</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>148633</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>151769</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,49%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,93%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>141607</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>135925</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>144723</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,43%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>92,56%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,55%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>407</t>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>286757</t>
+          <t>286991</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>295821</t>
+          <t>296074</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>146847</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>146847</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>146847</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>151769</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>151769</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>151769</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>146847</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>146847</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>146847</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9524</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5075</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16503</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>7422</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3692</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13046</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4139</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>9524</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>5013</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>16009</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10957</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>24821</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>660157</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>653178</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>664606</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,58%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>954</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>632923</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>627299</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>636653</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>626381</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>636206</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,84%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,96%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>660157</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>653672</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>664668</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1284980</t>
+          <t>1285204</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1299068</t>
+          <t>1299136</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>669681</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>669681</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>669681</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>965</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>640345</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>640345</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>640345</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>669681</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>669681</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>669681</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por dispensación de recetas en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si su última consulta médica fue por dispensación de recetas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>359</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>657</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15054</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13916</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15352</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,06%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,64%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15879</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14263</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16295</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,53%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>14708</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13260</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>15067</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>97,62%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>88,0%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18051</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16619</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>18447</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>90,09%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>68</t>
@@ -6752,27 +6752,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>33930</t>
+          <t>29762</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31650</t>
+          <t>28214</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34742</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15352</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15352</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15352</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>16295</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>16295</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16295</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>34742</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34742</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34742</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -7020,74 +7020,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28008</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24949</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>29146</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,09%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,6%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>27046</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>24615</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28198</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>95,91%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>24354</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>21880</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>25400</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>95,88%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>86,14%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>32416</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>29328</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>33728</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,11%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>86,95%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>92</t>
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>59461</t>
+          <t>52361</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56272</t>
+          <t>49254</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61298</t>
+          <t>53981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>29146</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>29146</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>29146</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>28198</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>28198</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>28198</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>61925</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>61925</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61925</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6800</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19,12%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3780</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3803</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,08%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5731</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>863</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7438</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -7363,74 +7363,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33651</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28763</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>35563</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,62%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>80,88%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>30508</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>27516</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>31296</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>97,48%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,92%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>28694</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>25751</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>29554</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>97,09%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>87,13%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>34950</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>31140</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>36871</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,79%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>84,46%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>82</t>
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>65458</t>
+          <t>62345</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61113</t>
+          <t>57679</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67396</t>
+          <t>64254</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35563</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35563</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35563</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>31296</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>31296</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>31296</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>29554</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>29554</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>29554</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>68167</t>
+          <t>65117</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>68167</t>
+          <t>65117</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>68167</t>
+          <t>65117</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2164</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9352</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2915</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2554</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2087</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9092</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>505</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -7706,74 +7706,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>39496</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>32308</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,8%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>23986</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>21611</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>24526</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>97,8%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>25012</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>22936</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>25490</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,12%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>89,98%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>40459</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>33454</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>42546</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,09%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>78,63%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>87</t>
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>64444</t>
+          <t>64507</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58844</t>
+          <t>57480</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66525</t>
+          <t>66645</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>24526</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>24526</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>24526</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>67150</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>67150</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>67150</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5513</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2435</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12689</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2896</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1150</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6645</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12110</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14847</t>
+          <t>14770</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>116209</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>109033</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>119287</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,58%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>97418</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>93669</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>99164</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>97,11%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>125876</t>
+          <t>92769</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119482</t>
+          <t>88494</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129204</t>
+          <t>94560</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>223294</t>
+          <t>208978</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>217059</t>
+          <t>202464</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>227611</t>
+          <t>212727</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
